--- a/outputs/monitor_xlsx/20260326.xlsx
+++ b/outputs/monitor_xlsx/20260326.xlsx
@@ -544,10 +544,6 @@
           <t>+2.54%</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -570,10 +566,6 @@
           <t>+3.88%</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -591,11 +583,6 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -618,10 +605,6 @@
           <t>+2.13%</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -644,10 +627,6 @@
           <t>-3.82%</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -670,10 +649,6 @@
           <t>+0.04%</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -696,10 +671,6 @@
           <t>-4.79%</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -722,10 +693,6 @@
           <t>+8.33%</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -748,10 +715,6 @@
           <t>+4.12%</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -769,7 +732,6 @@
           <t>-79.2億</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
           <t>-380.02億</t>
@@ -807,7 +769,6 @@
           <t>47.43億</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
           <t>29.57億</t>
@@ -818,8 +779,6 @@
           <t>147.84億</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -837,15 +796,11 @@
           <t>128.6%</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
           <t>127.35%</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -863,11 +818,6 @@
           <t>1.18億</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -885,15 +835,11 @@
           <t>7142口</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
           <t>10063口</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -911,7 +857,6 @@
           <t>39.17億</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
           <t>4.89億</t>
@@ -1016,10 +961,6 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr"/>
-      <c r="B8" t="inlineStr"/>
-    </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
@@ -1141,7 +1082,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W18"/>
+  <dimension ref="A1:W20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1176,6 +1117,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
@@ -2229,6 +2171,112 @@
       <c r="W18" t="inlineStr">
         <is>
           <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>6515</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>穎崴</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>8145</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>-3.61</v>
+      </c>
+      <c r="E19" t="n">
+        <v>150</v>
+      </c>
+      <c r="F19" s="7" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G19" t="n">
+        <v>129</v>
+      </c>
+      <c r="H19" t="n">
+        <v>-14</v>
+      </c>
+      <c r="I19" t="n">
+        <v>-62</v>
+      </c>
+      <c r="J19" t="n">
+        <v>9</v>
+      </c>
+      <c r="K19" t="n">
+        <v>292</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1376</v>
+      </c>
+      <c r="M19" t="n">
+        <v>-8983</v>
+      </c>
+      <c r="N19" t="n">
+        <v>29.34</v>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>中性</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2360</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>致茂</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>1640</v>
+      </c>
+      <c r="D20" s="7" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="E20" t="n">
+        <v>5841</v>
+      </c>
+      <c r="F20" s="7" t="n">
+        <v>-146</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-1069</v>
+      </c>
+      <c r="H20" t="n">
+        <v>70</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1975</v>
+      </c>
+      <c r="J20" t="n">
+        <v>141</v>
+      </c>
+      <c r="K20" t="n">
+        <v>2856</v>
+      </c>
+      <c r="L20" t="n">
+        <v>14470</v>
+      </c>
+      <c r="M20" t="n">
+        <v>-106311</v>
+      </c>
+      <c r="N20" t="n">
+        <v>11.34</v>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>偏空</t>
         </is>
       </c>
     </row>

--- a/outputs/monitor_xlsx/20260326.xlsx
+++ b/outputs/monitor_xlsx/20260326.xlsx
@@ -536,14 +536,18 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>33439.11</t>
+          <t>33337.62</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>+2.54%</t>
-        </is>
-      </c>
+          <t>-0.30%</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -558,14 +562,18 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>324.87</t>
+          <t>322.8</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>+3.88%</t>
-        </is>
-      </c>
+          <t>-0.64%</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -583,6 +591,11 @@
           <t>N/A</t>
         </is>
       </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -605,6 +618,10 @@
           <t>+2.13%</t>
         </is>
       </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -619,14 +636,18 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>4376.0$</t>
+          <t>4375.5$</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>-3.82%</t>
-        </is>
-      </c>
+          <t>-3.83%</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -649,6 +670,10 @@
           <t>+0.04%</t>
         </is>
       </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -671,6 +696,10 @@
           <t>-4.79%</t>
         </is>
       </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -693,6 +722,10 @@
           <t>+8.33%</t>
         </is>
       </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -707,14 +740,18 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>94.04$</t>
+          <t>94.48$</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>+4.12%</t>
-        </is>
-      </c>
+          <t>+4.61%</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -732,24 +769,25 @@
           <t>-79.2億</t>
         </is>
       </c>
+      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>-380.02億</t>
+          <t>-228.02億</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-1900.12億</t>
+          <t>-1140.1億</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-374.34億</t>
+          <t>None億</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-7486.71億</t>
+          <t>None億</t>
         </is>
       </c>
     </row>
@@ -769,16 +807,19 @@
           <t>47.43億</t>
         </is>
       </c>
+      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>29.57億</t>
+          <t>39.75億</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>147.84億</t>
-        </is>
-      </c>
+          <t>198.74億</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -793,14 +834,18 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>128.6%</t>
-        </is>
-      </c>
+          <t>141.14%</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
           <t>127.35%</t>
         </is>
       </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -818,6 +863,11 @@
           <t>1.18億</t>
         </is>
       </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -835,11 +885,15 @@
           <t>7142口</t>
         </is>
       </c>
+      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>10063口</t>
-        </is>
-      </c>
+          <t>9035口</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -857,24 +911,25 @@
           <t>39.17億</t>
         </is>
       </c>
+      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>4.89億</t>
+          <t>17.92億</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>24.43億</t>
+          <t>89.6億</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-14.16億</t>
+          <t>-12.94億</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-283.19億</t>
+          <t>-258.71億</t>
         </is>
       </c>
     </row>
@@ -921,7 +976,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-380.02億</t>
+          <t>-228.02億</t>
         </is>
       </c>
     </row>
@@ -933,7 +988,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>-1900.12億</t>
+          <t>-1140.1億</t>
         </is>
       </c>
     </row>
@@ -945,7 +1000,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-374.34億</t>
+          <t>None億</t>
         </is>
       </c>
     </row>
@@ -957,9 +1012,13 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>-7486.71億</t>
-        </is>
-      </c>
+          <t>None億</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr"/>
+      <c r="B8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -969,7 +1028,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>29.57億</t>
+          <t>39.75億</t>
         </is>
       </c>
     </row>
@@ -981,7 +1040,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>147.84億</t>
+          <t>198.74億</t>
         </is>
       </c>
     </row>
@@ -1000,7 +1059,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>4.89億</t>
+          <t>17.92億</t>
         </is>
       </c>
     </row>
@@ -1012,7 +1071,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>24.43億</t>
+          <t>89.6億</t>
         </is>
       </c>
     </row>
@@ -1024,7 +1083,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>-14.16億</t>
+          <t>-12.94億</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1095,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>-283.19億</t>
+          <t>-258.71億</t>
         </is>
       </c>
     </row>
@@ -1067,7 +1126,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>10063口</t>
+          <t>9035口</t>
         </is>
       </c>
     </row>
@@ -1082,7 +1141,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W20"/>
+  <dimension ref="A1:V16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1100,14 +1159,13 @@
     <col width="12" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
     <col width="12" customWidth="1" min="15" max="15"/>
-    <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
     <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="12" customWidth="1" min="20" max="20"/>
-    <col width="10" customWidth="1" min="21" max="21"/>
-    <col width="12" customWidth="1" min="22" max="22"/>
-    <col width="10" customWidth="1" min="23" max="23"/>
+    <col width="12" customWidth="1" min="19" max="19"/>
+    <col width="10" customWidth="1" min="20" max="20"/>
+    <col width="12" customWidth="1" min="21" max="21"/>
+    <col width="10" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1117,7 +1175,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
@@ -1196,40 +1253,35 @@
       </c>
       <c r="P3" s="5" t="inlineStr">
         <is>
-          <t>籌碼評價</t>
+          <t>買賣券商差</t>
         </is>
       </c>
       <c r="Q3" s="5" t="inlineStr">
         <is>
-          <t>買賣券商差</t>
+          <t>籌碼集中度5D(%)</t>
         </is>
       </c>
       <c r="R3" s="5" t="inlineStr">
         <is>
-          <t>籌碼集中度5D(%)</t>
+          <t>借券賣出餘額</t>
         </is>
       </c>
       <c r="S3" s="5" t="inlineStr">
         <is>
-          <t>借券賣出餘額</t>
+          <t>短回補天數</t>
         </is>
       </c>
       <c r="T3" s="5" t="inlineStr">
         <is>
-          <t>短回補天數</t>
+          <t>VWAP20D</t>
         </is>
       </c>
       <c r="U3" s="5" t="inlineStr">
         <is>
-          <t>VWAP20D</t>
+          <t>VWAP乖離(%)</t>
         </is>
       </c>
       <c r="V3" s="5" t="inlineStr">
-        <is>
-          <t>VWAP乖離(%)</t>
-        </is>
-      </c>
-      <c r="W3" s="5" t="inlineStr">
         <is>
           <t>資料來源</t>
         </is>
@@ -1264,7 +1316,7 @@
         <v>-30484</v>
       </c>
       <c r="H4" t="n">
-        <v>-233005</v>
+        <v>-143834</v>
       </c>
       <c r="I4" t="n">
         <v>1900</v>
@@ -1279,20 +1331,12 @@
         <v>12601</v>
       </c>
       <c r="M4" t="n">
-        <v>66986</v>
+        <v>53816</v>
       </c>
       <c r="N4" t="n">
         <v>-4545472</v>
       </c>
-      <c r="O4" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1327,13 +1371,13 @@
         <v>-831</v>
       </c>
       <c r="H5" t="n">
-        <v>130</v>
+        <v>99</v>
       </c>
       <c r="I5" t="n">
         <v>-1</v>
       </c>
       <c r="J5" t="n">
-        <v>-9</v>
+        <v>15</v>
       </c>
       <c r="K5" t="n">
         <v>183</v>
@@ -1342,20 +1386,12 @@
         <v>2772</v>
       </c>
       <c r="M5" t="n">
-        <v>14236</v>
+        <v>11351</v>
       </c>
       <c r="N5" t="n">
         <v>-78867</v>
       </c>
-      <c r="O5" t="n">
-        <v>-1.43</v>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1390,13 +1426,13 @@
         <v>-1555</v>
       </c>
       <c r="H6" t="n">
-        <v>9481</v>
+        <v>8289</v>
       </c>
       <c r="I6" t="n">
         <v>387</v>
       </c>
       <c r="J6" t="n">
-        <v>239</v>
+        <v>365</v>
       </c>
       <c r="K6" t="n">
         <v>253</v>
@@ -1405,20 +1441,12 @@
         <v>5657</v>
       </c>
       <c r="M6" t="n">
-        <v>27626</v>
+        <v>22334</v>
       </c>
       <c r="N6" t="n">
         <v>-649375</v>
       </c>
-      <c r="O6" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>偏多</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1453,13 +1481,13 @@
         <v>-5191</v>
       </c>
       <c r="H7" t="n">
-        <v>-49064</v>
+        <v>-26274</v>
       </c>
       <c r="I7" t="n">
         <v>548</v>
       </c>
       <c r="J7" t="n">
-        <v>-1311</v>
+        <v>-1211</v>
       </c>
       <c r="K7" t="n">
         <v>305</v>
@@ -1468,20 +1496,12 @@
         <v>26577</v>
       </c>
       <c r="M7" t="n">
-        <v>131372</v>
+        <v>105103</v>
       </c>
       <c r="N7" t="n">
         <v>-6483130</v>
       </c>
-      <c r="O7" t="n">
-        <v>0.49</v>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>主力積極賣出</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1490,12 +1510,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1504,47 +1524,39 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>96</v>
+        <v>1675</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>-2.24</v>
+        <v>-0.59</v>
       </c>
       <c r="F8" t="n">
-        <v>190169</v>
-      </c>
-      <c r="G8" s="7" t="n">
-        <v>-4838</v>
+        <v>7062</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>865</v>
       </c>
       <c r="H8" t="n">
-        <v>-227129</v>
+        <v>-757</v>
       </c>
       <c r="I8" t="n">
-        <v>-6044</v>
+        <v>149</v>
       </c>
       <c r="J8" t="n">
-        <v>40235</v>
+        <v>559</v>
       </c>
       <c r="K8" t="n">
-        <v>2958</v>
+        <v>172</v>
       </c>
       <c r="L8" t="n">
-        <v>129233</v>
+        <v>1911</v>
       </c>
       <c r="M8" t="n">
-        <v>659354</v>
+        <v>9721</v>
       </c>
       <c r="N8" t="n">
-        <v>-1125000</v>
-      </c>
-      <c r="O8" t="n">
-        <v>-10.65</v>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
+        <v>-140191</v>
+      </c>
+      <c r="V8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1553,12 +1565,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2383</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>台光電</t>
+          <t>致茂</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1567,47 +1579,39 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2945</v>
+        <v>1640</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>3.51</v>
+        <v>0.92</v>
       </c>
       <c r="F9" t="n">
-        <v>4555</v>
-      </c>
-      <c r="G9" s="6" t="n">
-        <v>463</v>
+        <v>5841</v>
+      </c>
+      <c r="G9" s="7" t="n">
+        <v>-146</v>
       </c>
       <c r="H9" t="n">
-        <v>-103</v>
+        <v>-923</v>
       </c>
       <c r="I9" t="n">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="J9" t="n">
-        <v>414</v>
+        <v>1905</v>
       </c>
       <c r="K9" t="n">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="L9" t="n">
-        <v>1839</v>
+        <v>2856</v>
       </c>
       <c r="M9" t="n">
-        <v>9860</v>
+        <v>11614</v>
       </c>
       <c r="N9" t="n">
-        <v>-89562</v>
-      </c>
-      <c r="O9" t="n">
-        <v>4.99</v>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
+        <v>-106311</v>
+      </c>
+      <c r="V9" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1616,12 +1620,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>6442</t>
+          <t>2383</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>光聖</t>
+          <t>台光電</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1630,47 +1634,39 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2080</v>
-      </c>
-      <c r="E10" s="6" t="n">
-        <v>-2.12</v>
+        <v>2945</v>
+      </c>
+      <c r="E10" s="7" t="n">
+        <v>3.51</v>
       </c>
       <c r="F10" t="n">
-        <v>4949</v>
-      </c>
-      <c r="G10" s="7" t="n">
-        <v>-479</v>
+        <v>4555</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>463</v>
       </c>
       <c r="H10" t="n">
-        <v>-555</v>
+        <v>-866</v>
       </c>
       <c r="I10" t="n">
-        <v>276</v>
+        <v>57</v>
       </c>
       <c r="J10" t="n">
-        <v>993</v>
+        <v>468</v>
       </c>
       <c r="K10" t="n">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="L10" t="n">
-        <v>3912</v>
+        <v>1839</v>
       </c>
       <c r="M10" t="n">
-        <v>20853</v>
+        <v>8012</v>
       </c>
       <c r="N10" t="n">
-        <v>-19483</v>
-      </c>
-      <c r="O10" t="n">
-        <v>5.21</v>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
+        <v>-89562</v>
+      </c>
+      <c r="V10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1679,61 +1675,53 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>6442</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>聯亞</t>
+          <t>光聖</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>上櫃</t>
+          <t>上市</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1690</v>
-      </c>
-      <c r="E11" s="7" t="n">
-        <v>9.74</v>
+        <v>2080</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>-2.12</v>
       </c>
       <c r="F11" t="n">
-        <v>4150</v>
-      </c>
-      <c r="G11" s="6" t="n">
-        <v>170</v>
+        <v>4949</v>
+      </c>
+      <c r="G11" s="7" t="n">
+        <v>-479</v>
       </c>
       <c r="H11" t="n">
-        <v>179</v>
+        <v>-560</v>
       </c>
       <c r="I11" t="n">
-        <v>580</v>
+        <v>276</v>
       </c>
       <c r="J11" t="n">
-        <v>8</v>
+        <v>950</v>
       </c>
       <c r="K11" t="n">
-        <v>-221</v>
+        <v>141</v>
       </c>
       <c r="L11" t="n">
-        <v>180</v>
+        <v>3912</v>
       </c>
       <c r="M11" t="n">
-        <v>-329</v>
+        <v>16746</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>主力積極買進</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
+        <v>-19483</v>
+      </c>
+      <c r="V11" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1742,61 +1730,53 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>4979</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>華星光</t>
+          <t>穎崴</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>上櫃</t>
+          <t>上市</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>411</v>
+        <v>8145</v>
       </c>
       <c r="E12" s="6" t="n">
-        <v>-3.41</v>
+        <v>-3.61</v>
       </c>
       <c r="F12" t="n">
-        <v>32812</v>
+        <v>150</v>
       </c>
       <c r="G12" s="7" t="n">
-        <v>-897</v>
+        <v>-1</v>
       </c>
       <c r="H12" t="n">
-        <v>4154</v>
+        <v>130</v>
       </c>
       <c r="I12" t="n">
-        <v>272</v>
+        <v>-14</v>
       </c>
       <c r="J12" t="n">
-        <v>2686</v>
+        <v>-48</v>
       </c>
       <c r="K12" t="n">
-        <v>-81</v>
+        <v>9</v>
       </c>
       <c r="L12" t="n">
-        <v>-1804</v>
+        <v>292</v>
       </c>
       <c r="M12" t="n">
-        <v>1402</v>
+        <v>1084</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>偏多</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
+        <v>-8983</v>
+      </c>
+      <c r="V12" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1805,61 +1785,53 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>聯亞</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>上市</t>
+          <t>上櫃</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1675</v>
-      </c>
-      <c r="E13" s="6" t="n">
-        <v>-0.59</v>
+        <v>2315</v>
+      </c>
+      <c r="E13" s="7" t="n">
+        <v>9.98</v>
       </c>
       <c r="F13" t="n">
-        <v>7062</v>
+        <v>2730</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>865</v>
+        <v>170</v>
       </c>
       <c r="H13" t="n">
-        <v>-884</v>
+        <v>63</v>
       </c>
       <c r="I13" t="n">
-        <v>149</v>
+        <v>580</v>
       </c>
       <c r="J13" t="n">
-        <v>804</v>
+        <v>-2</v>
       </c>
       <c r="K13" t="n">
-        <v>172</v>
+        <v>-221</v>
       </c>
       <c r="L13" t="n">
-        <v>1911</v>
+        <v>180</v>
       </c>
       <c r="M13" t="n">
-        <v>11971</v>
+        <v>-287</v>
       </c>
       <c r="N13" t="n">
-        <v>-140191</v>
-      </c>
-      <c r="O13" t="n">
-        <v>4.88</v>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="W13" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="V13" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1868,12 +1840,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>3163</t>
+          <t>4979</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>波若威</t>
+          <t>華星光</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1882,47 +1854,39 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>809</v>
-      </c>
-      <c r="E14" s="6" t="n">
-        <v>-9.91</v>
+        <v>449.5</v>
+      </c>
+      <c r="E14" s="7" t="n">
+        <v>4.78</v>
       </c>
       <c r="F14" t="n">
-        <v>945</v>
+        <v>3871</v>
       </c>
       <c r="G14" s="7" t="n">
-        <v>-63</v>
+        <v>-897</v>
       </c>
       <c r="H14" t="n">
-        <v>3</v>
+        <v>4438</v>
       </c>
       <c r="I14" t="n">
-        <v>-31</v>
+        <v>272</v>
       </c>
       <c r="J14" t="n">
-        <v>78</v>
+        <v>2618</v>
       </c>
       <c r="K14" t="n">
-        <v>33</v>
+        <v>-81</v>
       </c>
       <c r="L14" t="n">
-        <v>-91</v>
+        <v>-1804</v>
       </c>
       <c r="M14" t="n">
-        <v>-583</v>
+        <v>1369</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>主力積極買進</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1945,19 +1909,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>939</v>
-      </c>
-      <c r="E15" s="6" t="n">
-        <v>-1.68</v>
+        <v>974</v>
+      </c>
+      <c r="E15" s="7" t="n">
+        <v>9.93</v>
       </c>
       <c r="F15" t="n">
-        <v>9737</v>
+        <v>1350</v>
       </c>
       <c r="G15" s="6" t="n">
         <v>285</v>
       </c>
       <c r="H15" t="n">
-        <v>-2967</v>
+        <v>-3270</v>
       </c>
       <c r="I15" t="n">
         <v>544</v>
@@ -1972,20 +1936,12 @@
         <v>-551</v>
       </c>
       <c r="M15" t="n">
-        <v>1057</v>
+        <v>1162</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1994,289 +1950,55 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>3030</t>
+          <t>6640</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>德律</t>
+          <t>均華</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>上市</t>
+          <t>上櫃</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>253</v>
+        <v>1600</v>
       </c>
       <c r="E16" s="7" t="n">
-        <v>0.8</v>
+        <v>4.92</v>
       </c>
       <c r="F16" t="n">
-        <v>3859</v>
-      </c>
-      <c r="G16" s="7" t="n">
-        <v>-419</v>
+        <v>904</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>68</v>
       </c>
       <c r="H16" t="n">
-        <v>1117</v>
+        <v>157</v>
       </c>
       <c r="I16" t="n">
-        <v>-3</v>
+        <v>-10</v>
       </c>
       <c r="J16" t="n">
-        <v>-14</v>
+        <v>-6</v>
       </c>
       <c r="K16" t="n">
-        <v>86</v>
+        <v>-20</v>
       </c>
       <c r="L16" t="n">
-        <v>6444</v>
+        <v>27</v>
       </c>
       <c r="M16" t="n">
-        <v>32553</v>
+        <v>-132</v>
       </c>
       <c r="N16" t="n">
-        <v>-59048</v>
-      </c>
-      <c r="O16" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="V16" t="inlineStr">
         <is>
           <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>1305</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>華夏</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="E17" s="7" t="n">
-        <v>7.17</v>
-      </c>
-      <c r="F17" t="n">
-        <v>28698</v>
-      </c>
-      <c r="G17" s="7" t="n">
-        <v>-773</v>
-      </c>
-      <c r="H17" t="n">
-        <v>1270</v>
-      </c>
-      <c r="J17" t="n">
-        <v>200</v>
-      </c>
-      <c r="K17" t="n">
-        <v>17</v>
-      </c>
-      <c r="L17" t="n">
-        <v>8115</v>
-      </c>
-      <c r="M17" t="n">
-        <v>38200</v>
-      </c>
-      <c r="N17" t="n">
-        <v>-145240</v>
-      </c>
-      <c r="O17" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>偏多</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>1309</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>台達化</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>20.15</v>
-      </c>
-      <c r="E18" s="7" t="n">
-        <v>9.81</v>
-      </c>
-      <c r="F18" t="n">
-        <v>11922</v>
-      </c>
-      <c r="G18" s="6" t="n">
-        <v>3429</v>
-      </c>
-      <c r="H18" t="n">
-        <v>5199</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>3</v>
-      </c>
-      <c r="L18" t="n">
-        <v>9016</v>
-      </c>
-      <c r="M18" t="n">
-        <v>39157</v>
-      </c>
-      <c r="N18" t="n">
-        <v>-99265</v>
-      </c>
-      <c r="O18" t="n">
-        <v>7.75</v>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>偏多</t>
-        </is>
-      </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>6515</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>穎崴</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>8145</v>
-      </c>
-      <c r="D19" s="6" t="n">
-        <v>-3.61</v>
-      </c>
-      <c r="E19" t="n">
-        <v>150</v>
-      </c>
-      <c r="F19" s="7" t="n">
-        <v>-1</v>
-      </c>
-      <c r="G19" t="n">
-        <v>129</v>
-      </c>
-      <c r="H19" t="n">
-        <v>-14</v>
-      </c>
-      <c r="I19" t="n">
-        <v>-62</v>
-      </c>
-      <c r="J19" t="n">
-        <v>9</v>
-      </c>
-      <c r="K19" t="n">
-        <v>292</v>
-      </c>
-      <c r="L19" t="n">
-        <v>1376</v>
-      </c>
-      <c r="M19" t="n">
-        <v>-8983</v>
-      </c>
-      <c r="N19" t="n">
-        <v>29.34</v>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>2360</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>致茂</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>1640</v>
-      </c>
-      <c r="D20" s="7" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="E20" t="n">
-        <v>5841</v>
-      </c>
-      <c r="F20" s="7" t="n">
-        <v>-146</v>
-      </c>
-      <c r="G20" t="n">
-        <v>-1069</v>
-      </c>
-      <c r="H20" t="n">
-        <v>70</v>
-      </c>
-      <c r="I20" t="n">
-        <v>1975</v>
-      </c>
-      <c r="J20" t="n">
-        <v>141</v>
-      </c>
-      <c r="K20" t="n">
-        <v>2856</v>
-      </c>
-      <c r="L20" t="n">
-        <v>14470</v>
-      </c>
-      <c r="M20" t="n">
-        <v>-106311</v>
-      </c>
-      <c r="N20" t="n">
-        <v>11.34</v>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>偏空</t>
         </is>
       </c>
     </row>

--- a/outputs/monitor_xlsx/20260326.xlsx
+++ b/outputs/monitor_xlsx/20260326.xlsx
@@ -544,10 +544,6 @@
           <t>-0.30%</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -570,10 +566,6 @@
           <t>-0.64%</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -591,11 +583,6 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -618,10 +605,6 @@
           <t>+2.13%</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -644,10 +627,6 @@
           <t>-3.83%</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -670,10 +649,6 @@
           <t>+0.04%</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -696,10 +671,6 @@
           <t>-4.79%</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -722,10 +693,6 @@
           <t>+8.33%</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -748,10 +715,6 @@
           <t>+4.61%</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -769,7 +732,6 @@
           <t>-79.2億</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
           <t>-228.02億</t>
@@ -807,7 +769,6 @@
           <t>47.43億</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
           <t>39.75億</t>
@@ -818,8 +779,6 @@
           <t>198.74億</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -837,15 +796,11 @@
           <t>141.14%</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
           <t>127.35%</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -863,11 +818,6 @@
           <t>1.18億</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -885,15 +835,11 @@
           <t>7142口</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
           <t>9035口</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -911,7 +857,6 @@
           <t>39.17億</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
           <t>17.92億</t>
@@ -1016,10 +961,7 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr"/>
-      <c r="B8" t="inlineStr"/>
-    </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
@@ -1141,7 +1083,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V16"/>
+  <dimension ref="A1:V17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1175,6 +1117,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
@@ -2000,6 +1943,54 @@
         <is>
           <t>N/A</t>
         </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>3167</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>大量</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>349.5</v>
+      </c>
+      <c r="D17" s="7" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="E17" t="n">
+        <v>639</v>
+      </c>
+      <c r="F17" s="7" t="n">
+        <v>-42</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-216</v>
+      </c>
+      <c r="H17" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I17" t="n">
+        <v>25</v>
+      </c>
+      <c r="J17" t="n">
+        <v>26</v>
+      </c>
+      <c r="K17" t="n">
+        <v>7942</v>
+      </c>
+      <c r="L17" t="n">
+        <v>40805</v>
+      </c>
+      <c r="M17" t="n">
+        <v>-22128</v>
+      </c>
+      <c r="N17" t="n">
+        <v>9.890000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/monitor_xlsx/20260326.xlsx
+++ b/outputs/monitor_xlsx/20260326.xlsx
@@ -961,7 +961,6 @@
         </is>
       </c>
     </row>
-    <row r="8"/>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
@@ -1238,7 +1237,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0050</t>
+          <t>元大台灣50</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1246,7 +1245,7 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D4" t="n">
+      <c r="D4" s="6" t="n">
         <v>75.8</v>
       </c>
       <c r="E4" s="6" t="n">
@@ -1259,13 +1258,13 @@
         <v>-30484</v>
       </c>
       <c r="H4" t="n">
-        <v>-143834</v>
+        <v>-174318</v>
       </c>
       <c r="I4" t="n">
         <v>1900</v>
       </c>
       <c r="J4" t="n">
-        <v>130</v>
+        <v>2030</v>
       </c>
       <c r="K4" t="n">
         <v>5303</v>
@@ -1274,11 +1273,14 @@
         <v>12601</v>
       </c>
       <c r="M4" t="n">
-        <v>53816</v>
+        <v>66417</v>
       </c>
       <c r="N4" t="n">
         <v>-4545472</v>
       </c>
+      <c r="O4" t="n">
+        <v>-1.06</v>
+      </c>
       <c r="V4" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1301,7 +1303,7 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D5" t="n">
+      <c r="D5" s="6" t="n">
         <v>894</v>
       </c>
       <c r="E5" s="6" t="n">
@@ -1314,13 +1316,13 @@
         <v>-831</v>
       </c>
       <c r="H5" t="n">
-        <v>99</v>
+        <v>-732</v>
       </c>
       <c r="I5" t="n">
         <v>-1</v>
       </c>
       <c r="J5" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K5" t="n">
         <v>183</v>
@@ -1329,11 +1331,14 @@
         <v>2772</v>
       </c>
       <c r="M5" t="n">
-        <v>11351</v>
+        <v>14123</v>
       </c>
       <c r="N5" t="n">
         <v>-78867</v>
       </c>
+      <c r="O5" t="n">
+        <v>-3.95</v>
+      </c>
       <c r="V5" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1356,7 +1361,7 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D6" t="n">
+      <c r="D6" s="6" t="n">
         <v>1515</v>
       </c>
       <c r="E6" s="6" t="n">
@@ -1369,13 +1374,13 @@
         <v>-1555</v>
       </c>
       <c r="H6" t="n">
-        <v>8289</v>
+        <v>6734</v>
       </c>
       <c r="I6" t="n">
         <v>387</v>
       </c>
       <c r="J6" t="n">
-        <v>365</v>
+        <v>751</v>
       </c>
       <c r="K6" t="n">
         <v>253</v>
@@ -1384,11 +1389,14 @@
         <v>5657</v>
       </c>
       <c r="M6" t="n">
-        <v>22334</v>
+        <v>27991</v>
       </c>
       <c r="N6" t="n">
         <v>-649375</v>
       </c>
+      <c r="O6" t="n">
+        <v>8.779999999999999</v>
+      </c>
       <c r="V6" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1411,7 +1419,7 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D7" t="n">
+      <c r="D7" s="6" t="n">
         <v>1840</v>
       </c>
       <c r="E7" s="6" t="n">
@@ -1424,13 +1432,13 @@
         <v>-5191</v>
       </c>
       <c r="H7" t="n">
-        <v>-26274</v>
+        <v>-31465</v>
       </c>
       <c r="I7" t="n">
         <v>548</v>
       </c>
       <c r="J7" t="n">
-        <v>-1211</v>
+        <v>-664</v>
       </c>
       <c r="K7" t="n">
         <v>305</v>
@@ -1439,11 +1447,14 @@
         <v>26577</v>
       </c>
       <c r="M7" t="n">
-        <v>105103</v>
+        <v>131680</v>
       </c>
       <c r="N7" t="n">
         <v>-6483130</v>
       </c>
+      <c r="O7" t="n">
+        <v>-1.93</v>
+      </c>
       <c r="V7" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1466,7 +1477,7 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D8" t="n">
+      <c r="D8" s="6" t="n">
         <v>1675</v>
       </c>
       <c r="E8" s="6" t="n">
@@ -1479,13 +1490,13 @@
         <v>865</v>
       </c>
       <c r="H8" t="n">
-        <v>-757</v>
+        <v>108</v>
       </c>
       <c r="I8" t="n">
         <v>149</v>
       </c>
       <c r="J8" t="n">
-        <v>559</v>
+        <v>708</v>
       </c>
       <c r="K8" t="n">
         <v>172</v>
@@ -1494,11 +1505,14 @@
         <v>1911</v>
       </c>
       <c r="M8" t="n">
-        <v>9721</v>
+        <v>11632</v>
       </c>
       <c r="N8" t="n">
         <v>-140191</v>
       </c>
+      <c r="O8" t="n">
+        <v>12.59</v>
+      </c>
       <c r="V8" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1521,7 +1535,7 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D9" t="n">
+      <c r="D9" s="7" t="n">
         <v>1640</v>
       </c>
       <c r="E9" s="7" t="n">
@@ -1534,13 +1548,13 @@
         <v>-146</v>
       </c>
       <c r="H9" t="n">
-        <v>-923</v>
+        <v>-1069</v>
       </c>
       <c r="I9" t="n">
         <v>70</v>
       </c>
       <c r="J9" t="n">
-        <v>1905</v>
+        <v>1975</v>
       </c>
       <c r="K9" t="n">
         <v>141</v>
@@ -1549,11 +1563,14 @@
         <v>2856</v>
       </c>
       <c r="M9" t="n">
-        <v>11614</v>
+        <v>14470</v>
       </c>
       <c r="N9" t="n">
         <v>-106311</v>
       </c>
+      <c r="O9" t="n">
+        <v>11.34</v>
+      </c>
       <c r="V9" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1576,7 +1593,7 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D10" t="n">
+      <c r="D10" s="7" t="n">
         <v>2945</v>
       </c>
       <c r="E10" s="7" t="n">
@@ -1589,13 +1606,13 @@
         <v>463</v>
       </c>
       <c r="H10" t="n">
-        <v>-866</v>
+        <v>-403</v>
       </c>
       <c r="I10" t="n">
         <v>57</v>
       </c>
       <c r="J10" t="n">
-        <v>468</v>
+        <v>525</v>
       </c>
       <c r="K10" t="n">
         <v>149</v>
@@ -1604,11 +1621,14 @@
         <v>1839</v>
       </c>
       <c r="M10" t="n">
-        <v>8012</v>
+        <v>9851</v>
       </c>
       <c r="N10" t="n">
         <v>-89562</v>
       </c>
+      <c r="O10" t="n">
+        <v>14.78</v>
+      </c>
       <c r="V10" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1631,7 +1651,7 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D11" t="n">
+      <c r="D11" s="6" t="n">
         <v>2080</v>
       </c>
       <c r="E11" s="6" t="n">
@@ -1644,13 +1664,13 @@
         <v>-479</v>
       </c>
       <c r="H11" t="n">
-        <v>-560</v>
+        <v>-1039</v>
       </c>
       <c r="I11" t="n">
         <v>276</v>
       </c>
       <c r="J11" t="n">
-        <v>950</v>
+        <v>1225</v>
       </c>
       <c r="K11" t="n">
         <v>141</v>
@@ -1659,11 +1679,14 @@
         <v>3912</v>
       </c>
       <c r="M11" t="n">
-        <v>16746</v>
+        <v>20658</v>
       </c>
       <c r="N11" t="n">
         <v>-19483</v>
       </c>
+      <c r="O11" t="n">
+        <v>7.63</v>
+      </c>
       <c r="V11" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1686,7 +1709,7 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D12" t="n">
+      <c r="D12" s="6" t="n">
         <v>8145</v>
       </c>
       <c r="E12" s="6" t="n">
@@ -1699,13 +1722,13 @@
         <v>-1</v>
       </c>
       <c r="H12" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="I12" t="n">
         <v>-14</v>
       </c>
       <c r="J12" t="n">
-        <v>-48</v>
+        <v>-62</v>
       </c>
       <c r="K12" t="n">
         <v>9</v>
@@ -1714,11 +1737,14 @@
         <v>292</v>
       </c>
       <c r="M12" t="n">
-        <v>1084</v>
+        <v>1376</v>
       </c>
       <c r="N12" t="n">
         <v>-8983</v>
       </c>
+      <c r="O12" t="n">
+        <v>29.34</v>
+      </c>
       <c r="V12" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1741,26 +1767,26 @@
           <t>上櫃</t>
         </is>
       </c>
-      <c r="D13" t="n">
-        <v>2315</v>
+      <c r="D13" s="7" t="n">
+        <v>2365</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>9.98</v>
+        <v>2.16</v>
       </c>
       <c r="F13" t="n">
-        <v>2730</v>
+        <v>2182</v>
       </c>
       <c r="G13" s="6" t="n">
         <v>170</v>
       </c>
       <c r="H13" t="n">
-        <v>63</v>
+        <v>233</v>
       </c>
       <c r="I13" t="n">
         <v>580</v>
       </c>
       <c r="J13" t="n">
-        <v>-2</v>
+        <v>578</v>
       </c>
       <c r="K13" t="n">
         <v>-221</v>
@@ -1769,11 +1795,14 @@
         <v>180</v>
       </c>
       <c r="M13" t="n">
-        <v>-287</v>
+        <v>-107</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
       <c r="V13" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1796,26 +1825,26 @@
           <t>上櫃</t>
         </is>
       </c>
-      <c r="D14" t="n">
-        <v>449.5</v>
+      <c r="D14" s="7" t="n">
+        <v>586</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>4.78</v>
+        <v>9.94</v>
       </c>
       <c r="F14" t="n">
-        <v>3871</v>
+        <v>32773</v>
       </c>
       <c r="G14" s="7" t="n">
         <v>-897</v>
       </c>
       <c r="H14" t="n">
-        <v>4438</v>
+        <v>3541</v>
       </c>
       <c r="I14" t="n">
         <v>272</v>
       </c>
       <c r="J14" t="n">
-        <v>2618</v>
+        <v>2891</v>
       </c>
       <c r="K14" t="n">
         <v>-81</v>
@@ -1824,11 +1853,14 @@
         <v>-1804</v>
       </c>
       <c r="M14" t="n">
-        <v>1369</v>
+        <v>-435</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
       <c r="V14" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1851,26 +1883,26 @@
           <t>上櫃</t>
         </is>
       </c>
-      <c r="D15" t="n">
-        <v>974</v>
-      </c>
-      <c r="E15" s="7" t="n">
-        <v>9.93</v>
+      <c r="D15" s="6" t="n">
+        <v>1105</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>-2.64</v>
       </c>
       <c r="F15" t="n">
-        <v>1350</v>
+        <v>6341</v>
       </c>
       <c r="G15" s="6" t="n">
         <v>285</v>
       </c>
       <c r="H15" t="n">
-        <v>-3270</v>
+        <v>-2986</v>
       </c>
       <c r="I15" t="n">
         <v>544</v>
       </c>
       <c r="J15" t="n">
-        <v>4945</v>
+        <v>5489</v>
       </c>
       <c r="K15" t="n">
         <v>-92</v>
@@ -1879,11 +1911,14 @@
         <v>-551</v>
       </c>
       <c r="M15" t="n">
-        <v>1162</v>
+        <v>611</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
       <c r="V15" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1906,26 +1941,26 @@
           <t>上櫃</t>
         </is>
       </c>
-      <c r="D16" t="n">
-        <v>1600</v>
-      </c>
-      <c r="E16" s="7" t="n">
-        <v>4.92</v>
+      <c r="D16" s="6" t="n">
+        <v>1625</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>-6.07</v>
       </c>
       <c r="F16" t="n">
-        <v>904</v>
+        <v>1168</v>
       </c>
       <c r="G16" s="6" t="n">
         <v>68</v>
       </c>
       <c r="H16" t="n">
-        <v>157</v>
+        <v>226</v>
       </c>
       <c r="I16" t="n">
         <v>-10</v>
       </c>
       <c r="J16" t="n">
-        <v>-6</v>
+        <v>-16</v>
       </c>
       <c r="K16" t="n">
         <v>-20</v>
@@ -1934,11 +1969,14 @@
         <v>27</v>
       </c>
       <c r="M16" t="n">
-        <v>-132</v>
+        <v>-105</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
       </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
       <c r="V16" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1956,41 +1994,46 @@
           <t>大量</t>
         </is>
       </c>
-      <c r="C17" t="n">
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="n">
         <v>349.5</v>
       </c>
-      <c r="D17" s="7" t="n">
+      <c r="E17" s="7" t="n">
         <v>0.29</v>
       </c>
-      <c r="E17" t="n">
+      <c r="F17" s="7" t="n">
         <v>639</v>
       </c>
-      <c r="F17" s="7" t="n">
+      <c r="G17" s="7" t="n">
         <v>-42</v>
       </c>
-      <c r="G17" t="n">
-        <v>-216</v>
-      </c>
       <c r="H17" t="n">
+        <v>-282</v>
+      </c>
+      <c r="I17" t="n">
         <v>-1</v>
       </c>
-      <c r="I17" t="n">
+      <c r="J17" t="n">
         <v>25</v>
       </c>
-      <c r="J17" t="n">
+      <c r="K17" t="n">
         <v>26</v>
       </c>
-      <c r="K17" t="n">
+      <c r="L17" t="n">
         <v>7942</v>
       </c>
-      <c r="L17" t="n">
+      <c r="M17" t="n">
         <v>40805</v>
       </c>
-      <c r="M17" t="n">
+      <c r="N17" t="n">
         <v>-22128</v>
       </c>
-      <c r="N17" t="n">
-        <v>9.890000000000001</v>
+      <c r="O17" t="n">
+        <v>8.23</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/monitor_xlsx/20260326.xlsx
+++ b/outputs/monitor_xlsx/20260326.xlsx
@@ -1082,7 +1082,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V17"/>
+  <dimension ref="A1:V20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2036,6 +2036,165 @@
         <v>8.23</v>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2454</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>聯發科</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>1590</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>-1.85</v>
+      </c>
+      <c r="F18" t="n">
+        <v>7833</v>
+      </c>
+      <c r="G18" s="7" t="n">
+        <v>-2166</v>
+      </c>
+      <c r="H18" t="n">
+        <v>-3440</v>
+      </c>
+      <c r="I18" t="n">
+        <v>-339</v>
+      </c>
+      <c r="J18" t="n">
+        <v>-845</v>
+      </c>
+      <c r="K18" t="n">
+        <v>347</v>
+      </c>
+      <c r="L18" t="n">
+        <v>6255</v>
+      </c>
+      <c r="M18" t="n">
+        <v>30850</v>
+      </c>
+      <c r="N18" t="n">
+        <v>-400976</v>
+      </c>
+      <c r="O18" t="n">
+        <v>-7.39</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>3037</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>欣興</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>502</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>-0.79</v>
+      </c>
+      <c r="F19" t="n">
+        <v>8065</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>832</v>
+      </c>
+      <c r="H19" t="n">
+        <v>4767</v>
+      </c>
+      <c r="I19" t="n">
+        <v>-492</v>
+      </c>
+      <c r="J19" t="n">
+        <v>-2410</v>
+      </c>
+      <c r="K19" t="n">
+        <v>282</v>
+      </c>
+      <c r="L19" t="n">
+        <v>31201</v>
+      </c>
+      <c r="M19" t="n">
+        <v>161648</v>
+      </c>
+      <c r="N19" t="n">
+        <v>-393882</v>
+      </c>
+      <c r="O19" t="n">
+        <v>2.74</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>8046</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>南電</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>569</v>
+      </c>
+      <c r="E20" s="7" t="n">
+        <v>5.37</v>
+      </c>
+      <c r="F20" t="n">
+        <v>31163</v>
+      </c>
+      <c r="G20" s="6" t="n">
+        <v>4337</v>
+      </c>
+      <c r="H20" t="n">
+        <v>5313</v>
+      </c>
+      <c r="I20" t="n">
+        <v>2784</v>
+      </c>
+      <c r="J20" t="n">
+        <v>4029</v>
+      </c>
+      <c r="K20" t="n">
+        <v>632</v>
+      </c>
+      <c r="L20" t="n">
+        <v>8564</v>
+      </c>
+      <c r="M20" t="n">
+        <v>47946</v>
+      </c>
+      <c r="N20" t="n">
+        <v>-160884</v>
+      </c>
+      <c r="O20" t="n">
+        <v>12.15</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:O1"/>
